--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="95">
   <si>
     <t>Id</t>
   </si>
@@ -287,6 +287,36 @@
   </si>
   <si>
     <t>道戒等级上限+1</t>
+  </si>
+  <si>
+    <t>神宠契约</t>
+  </si>
+  <si>
+    <t>神宠等级上线+5</t>
+  </si>
+  <si>
+    <t>仙宠契约</t>
+  </si>
+  <si>
+    <t>仙宠等级上线+1</t>
+  </si>
+  <si>
+    <t>坐骑契约</t>
+  </si>
+  <si>
+    <t>坐骑等级上限+5</t>
+  </si>
+  <si>
+    <t>英灵契约</t>
+  </si>
+  <si>
+    <t>英灵等级上限+1</t>
+  </si>
+  <si>
+    <t>深渊契约</t>
+  </si>
+  <si>
+    <t>深渊等级上限+1</t>
   </si>
 </sst>
 </file>
@@ -1261,7 +1291,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J45"/>
+  <dimension ref="C3:J51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2338,6 +2368,145 @@
         <v>84</v>
       </c>
     </row>
+    <row r="46" customHeight="1" spans="3:10">
+      <c r="D46" s="4"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+    </row>
+    <row r="47" customHeight="1" spans="3:10">
+      <c r="C47" s="1">
+        <v>46</v>
+      </c>
+      <c r="D47" s="4">
+        <v>180046</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F47" s="1">
+        <v>46</v>
+      </c>
+      <c r="G47" s="6">
+        <v>5</v>
+      </c>
+      <c r="H47" s="1">
+        <v>10</v>
+      </c>
+      <c r="I47" s="1">
+        <v>8</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:10">
+      <c r="C48" s="1">
+        <v>47</v>
+      </c>
+      <c r="D48" s="4">
+        <v>180047</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F48" s="1">
+        <v>47</v>
+      </c>
+      <c r="G48" s="6">
+        <v>5</v>
+      </c>
+      <c r="H48" s="1">
+        <v>10</v>
+      </c>
+      <c r="I48" s="1">
+        <v>8</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:10">
+      <c r="C49" s="1">
+        <v>48</v>
+      </c>
+      <c r="D49" s="4">
+        <v>180048</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" s="1">
+        <v>48</v>
+      </c>
+      <c r="G49" s="6">
+        <v>5</v>
+      </c>
+      <c r="H49" s="1">
+        <v>10</v>
+      </c>
+      <c r="I49" s="1">
+        <v>8</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:10">
+      <c r="C50" s="1">
+        <v>49</v>
+      </c>
+      <c r="D50" s="4">
+        <v>180049</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50" s="1">
+        <v>49</v>
+      </c>
+      <c r="G50" s="6">
+        <v>1</v>
+      </c>
+      <c r="H50" s="1">
+        <v>10</v>
+      </c>
+      <c r="I50" s="1">
+        <v>8</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:10">
+      <c r="C51" s="1">
+        <v>50</v>
+      </c>
+      <c r="D51" s="4">
+        <v>180050</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F51" s="1">
+        <v>50</v>
+      </c>
+      <c r="G51" s="6">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1">
+        <v>10</v>
+      </c>
+      <c r="I51" s="1">
+        <v>8</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -292,19 +292,19 @@
     <t>神宠契约</t>
   </si>
   <si>
-    <t>神宠等级上线+5</t>
+    <t>神宠等级上限+5</t>
   </si>
   <si>
     <t>仙宠契约</t>
   </si>
   <si>
-    <t>仙宠等级上线+1</t>
+    <t>仙宠等级上限+5</t>
   </si>
   <si>
     <t>坐骑契约</t>
   </si>
   <si>
-    <t>坐骑等级上限+5</t>
+    <t>坐骑等级上限+3</t>
   </si>
   <si>
     <t>英灵契约</t>
@@ -2394,7 +2394,7 @@
         <v>5</v>
       </c>
       <c r="H47" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I47" s="1">
         <v>8</v>
@@ -2420,7 +2420,7 @@
         <v>5</v>
       </c>
       <c r="H48" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I48" s="1">
         <v>8</v>
@@ -2443,10 +2443,10 @@
         <v>48</v>
       </c>
       <c r="G49" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H49" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I49" s="1">
         <v>8</v>
